--- a/AAAGameData/Languages/ChineseSimplified.xlsx
+++ b/AAAGameData/Languages/ChineseSimplified.xlsx
@@ -430,6 +430,378 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -4245,7 +4617,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId146" name="A1">
+            <control shapeId="1056" r:id="rId236" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4267,7 +4639,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId147" name="A2">
+            <control shapeId="1057" r:id="rId237" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4289,7 +4661,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId148" name="A3">
+            <control shapeId="1058" r:id="rId238" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4311,7 +4683,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId149" name="A4">
+            <control shapeId="1059" r:id="rId239" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4333,7 +4705,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId150" name="A5">
+            <control shapeId="1060" r:id="rId240" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4355,7 +4727,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId151" name="A6">
+            <control shapeId="1061" r:id="rId241" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4377,7 +4749,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId152" name="A7">
+            <control shapeId="1062" r:id="rId242" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4399,7 +4771,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId153" name="A8">
+            <control shapeId="1063" r:id="rId243" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4421,7 +4793,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId154" name="A9">
+            <control shapeId="1064" r:id="rId244" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4443,7 +4815,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId155" name="A10">
+            <control shapeId="1065" r:id="rId245" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4465,7 +4837,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId156" name="A11">
+            <control shapeId="1066" r:id="rId246" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4487,7 +4859,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId157" name="A12">
+            <control shapeId="1067" r:id="rId247" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4509,7 +4881,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId158" name="A13">
+            <control shapeId="1068" r:id="rId248" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4531,7 +4903,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId159" name="A14">
+            <control shapeId="1069" r:id="rId249" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4553,7 +4925,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId160" name="A15">
+            <control shapeId="1070" r:id="rId250" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4575,7 +4947,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId161" name="A16">
+            <control shapeId="1071" r:id="rId251" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4597,7 +4969,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId162" name="A17">
+            <control shapeId="1072" r:id="rId252" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4619,7 +4991,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId163" name="A18">
+            <control shapeId="1073" r:id="rId253" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4641,7 +5013,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId164" name="A19">
+            <control shapeId="1074" r:id="rId254" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4663,7 +5035,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId165" name="A20">
+            <control shapeId="1075" r:id="rId255" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4685,7 +5057,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId166" name="A21">
+            <control shapeId="1076" r:id="rId256" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4707,7 +5079,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId167" name="A22">
+            <control shapeId="1077" r:id="rId257" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4729,7 +5101,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId168" name="A23">
+            <control shapeId="1078" r:id="rId258" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4751,7 +5123,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId169" name="A24">
+            <control shapeId="1079" r:id="rId259" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4773,7 +5145,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId170" name="A25">
+            <control shapeId="1080" r:id="rId260" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4795,7 +5167,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId171" name="A26">
+            <control shapeId="1081" r:id="rId261" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4817,7 +5189,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId172" name="A27">
+            <control shapeId="1082" r:id="rId262" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4839,7 +5211,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId173" name="A28">
+            <control shapeId="1083" r:id="rId263" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4861,7 +5233,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId174" name="A29">
+            <control shapeId="1084" r:id="rId264" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4883,7 +5255,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId175" name="A30">
+            <control shapeId="1085" r:id="rId265" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4905,7 +5277,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId176" name="A31">
+            <control shapeId="1086" r:id="rId266" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>

--- a/AAAGameData/Languages/ChineseSimplified.xlsx
+++ b/AAAGameData/Languages/ChineseSimplified.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>NoSaveData</t>
   </si>
@@ -187,6 +187,30 @@
   </si>
   <si>
     <t>继续</t>
+  </si>
+  <si>
+    <t>scene.base.name</t>
+  </si>
+  <si>
+    <t>基地</t>
+  </si>
+  <si>
+    <t>scene.world.name</t>
+  </si>
+  <si>
+    <t>大世界</t>
+  </si>
+  <si>
+    <t>scene.tutorial.name</t>
+  </si>
+  <si>
+    <t>某个实验室</t>
+  </si>
+  <si>
+    <t>scene.menu.name</t>
+  </si>
+  <si>
+    <t>主菜单</t>
   </si>
 </sst>
 </file>
@@ -199,7 +223,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -209,6 +233,13 @@
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -665,157 +696,160 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -984,7 +1018,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1050,8 +1084,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="182880"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="190500"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1117,8 +1151,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="365760"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="381000"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1184,8 +1218,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="548640"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="571500"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1251,8 +1285,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="731520"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="762000"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1318,8 +1352,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="914400"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="952500"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1385,8 +1419,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="1097280"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="1143000"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1452,8 +1486,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="1280160"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="1333500"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1519,8 +1553,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="1463040"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="1524000"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1586,8 +1620,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="1645920"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="1714500"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1653,8 +1687,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="1828800"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="1905000"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1720,8 +1754,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2011680"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="2095500"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1787,8 +1821,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2194560"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="2286000"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1854,8 +1888,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2377440"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="2476500"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1921,8 +1955,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2560320"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="2667000"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1988,8 +2022,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2743200"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="2857500"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2055,8 +2089,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2926080"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="3048000"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2122,8 +2156,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="3108960"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="3238500"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2189,8 +2223,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="3291840"/>
-              <a:ext cx="285750" cy="182880"/>
+              <a:off x="0" y="3429000"/>
+              <a:ext cx="285750" cy="190500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2489,8 +2523,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2666,6 +2700,38 @@
       </c>
       <c r="C19" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="B20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="B21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="B22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="B23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Languages/ChineseSimplified.xlsx
+++ b/AAAGameData/Languages/ChineseSimplified.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>NoSaveData</t>
   </si>
@@ -211,6 +211,48 @@
   </si>
   <si>
     <t>主菜单</t>
+  </si>
+  <si>
+    <t>scene.tiangong.name</t>
+  </si>
+  <si>
+    <t>天宫</t>
+  </si>
+  <si>
+    <t>scene.herheim.name</t>
+  </si>
+  <si>
+    <t>赫尔海默</t>
+  </si>
+  <si>
+    <t>scene.takamahara.name</t>
+  </si>
+  <si>
+    <t>高天原</t>
+  </si>
+  <si>
+    <t>scene.olympus.name</t>
+  </si>
+  <si>
+    <t>奥林匹斯山</t>
+  </si>
+  <si>
+    <t>scene.babylon.name</t>
+  </si>
+  <si>
+    <t>巴比伦空中花园</t>
+  </si>
+  <si>
+    <t>scene.avalon.name</t>
+  </si>
+  <si>
+    <t>阿瓦隆</t>
+  </si>
+  <si>
+    <t>scene.abyss.name</t>
+  </si>
+  <si>
+    <t>深渊之地</t>
   </si>
 </sst>
 </file>
@@ -696,19 +738,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -717,7 +759,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -841,13 +883,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1018,7 +1063,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1084,8 +1129,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="190500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="182880"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1151,8 +1196,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="381000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="365760"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1218,8 +1263,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="571500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="548640"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1285,8 +1330,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="762000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="731520"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1352,8 +1397,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="952500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="914400"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1419,8 +1464,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="1143000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="1097280"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1486,8 +1531,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="1333500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="1280160"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1553,8 +1598,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="1524000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="1463040"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1620,8 +1665,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="1714500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="1645920"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1687,8 +1732,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="1905000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="1828800"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1754,8 +1799,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2095500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="2011680"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1821,8 +1866,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2286000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="2194560"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1888,8 +1933,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2476500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="2377440"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1955,8 +2000,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2667000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="2560320"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2022,8 +2067,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="2857500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="2743200"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2089,8 +2134,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="3048000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="2926080"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2156,8 +2201,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="3238500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="3108960"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2223,8 +2268,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="3429000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off x="0" y="3291840"/>
+              <a:ext cx="285750" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2523,8 +2568,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2732,6 +2777,62 @@
       </c>
       <c r="C23" s="2" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="B24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="B25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" ht="27.6" spans="1:3">
+      <c r="B26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="B27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="B28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="B29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="B30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
